--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104753_W33.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104753_W33.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0847</v>
+        <v>4.1371</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2997</v>
+        <v>3.5403</v>
       </c>
       <c r="F2" t="n">
-        <v>0.785</v>
+        <v>0.5968</v>
       </c>
       <c r="G2" t="n">
         <v>-0.8741</v>
@@ -610,13 +610,13 @@
         <v>2.9592</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4353</v>
+        <v>0.4877</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9052</v>
+        <v>0.1457</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5301</v>
+        <v>0.3419</v>
       </c>
       <c r="V2" t="n">
         <v>1.792</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9954</v>
+        <v>2.1663</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4105</v>
+        <v>4.3618</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.4151</v>
+        <v>-2.1955</v>
       </c>
       <c r="G3" t="n">
         <v>2.2301</v>
@@ -688,13 +688,13 @@
         <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0769</v>
+        <v>0.094</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0229</v>
+        <v>-0.0258</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0998</v>
+        <v>0.1198</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1578</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4389</v>
+        <v>0.8569</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5659</v>
+        <v>-0.6146</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0048</v>
+        <v>1.4715</v>
       </c>
       <c r="G4" t="n">
         <v>-2.1802</v>
@@ -766,13 +766,13 @@
         <v>2.7316</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9362</v>
+        <v>0.3542</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3943</v>
+        <v>0.3456</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5419</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>1.0895</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. YUSTA</t>
+          <t>M. GONZALEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.244</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6149</v>
+        <v>0.0391</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6291</v>
+        <v>0.7376</v>
       </c>
       <c r="G5" t="n">
-        <v>-6.4038</v>
+        <v>-1.9898</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.3442</v>
+        <v>0.5423</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.0596</v>
+        <v>-2.5321</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.4902</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.0039</v>
+        <v>0.1551</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5135999999999999</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9136</v>
+        <v>-1.4298</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6597</v>
+        <v>0.3871</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.5733</v>
+        <v>-1.8169</v>
       </c>
       <c r="P5" t="n">
-        <v>2.9592</v>
+        <v>1.8211</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1868</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8754999999999999</v>
+        <v>-0.144</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9749</v>
+        <v>-0.2627</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0994</v>
+        <v>0.1187</v>
       </c>
       <c r="V5" t="n">
-        <v>3.8132</v>
+        <v>1.0895</v>
       </c>
       <c r="W5" t="n">
-        <v>4.3579</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5447</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. GONZALEZ</t>
+          <t>S. YUSTA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0693</v>
+        <v>0.6901</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3944</v>
+        <v>0.0924</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6748</v>
+        <v>0.5977</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.9898</v>
+        <v>-6.4038</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5423</v>
+        <v>-4.3442</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.5321</v>
+        <v>-2.0596</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-4.4902</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1551</v>
+        <v>-5.0039</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7151999999999999</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4298</v>
+        <v>-1.9136</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3871</v>
+        <v>0.6597</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.8169</v>
+        <v>-2.5733</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8211</v>
+        <v>2.9592</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0487</v>
+        <v>3.1868</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1486</v>
+        <v>0.3216</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0926</v>
+        <v>0.4523</v>
       </c>
       <c r="U6" t="n">
-        <v>0.056</v>
+        <v>-0.1308</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0895</v>
+        <v>3.8132</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0895</v>
+        <v>4.3579</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. STEPHENS</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8242</v>
+        <v>-0.5392</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4094</v>
+        <v>0.3401</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5853</v>
+        <v>-0.8793</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.9253</v>
+        <v>-0.8771</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0598</v>
+        <v>-0.1696</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8653999999999999</v>
+        <v>-0.7075</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9215</v>
+        <v>0.0545</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1691</v>
+        <v>0.0172</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7524</v>
+        <v>0.0372</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0037</v>
+        <v>-0.9315</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8907</v>
+        <v>-0.1868</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.113</v>
+        <v>-0.7447</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6829</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6829</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4182</v>
+        <v>0.3379</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4879</v>
+        <v>0.2856</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9061</v>
+        <v>0.0523</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>D. STEPHENS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9956</v>
+        <v>-0.8312</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0849</v>
+        <v>-1.1028</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9106</v>
+        <v>0.2716</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8771</v>
+        <v>-1.9253</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1696</v>
+        <v>-1.0598</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7075</v>
+        <v>-0.8653999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0545</v>
+        <v>-0.9215</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0172</v>
+        <v>-0.1691</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0372</v>
+        <v>-0.7524</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9315</v>
+        <v>-1.0037</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1868</v>
+        <v>-0.8907</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7447</v>
+        <v>-0.113</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1185</v>
+        <v>0.4112</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1394</v>
+        <v>-0.1813</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0209</v>
+        <v>0.5925</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8069</v>
+        <v>-1.6328</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0275</v>
+        <v>-1.0103</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7794</v>
+        <v>-0.6225000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>-3.059</v>
@@ -1156,13 +1156,13 @@
         <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1545</v>
+        <v>0.0196</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0455</v>
+        <v>-0.0283</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1089</v>
+        <v>0.0479</v>
       </c>
       <c r="V9" t="n">
         <v>1.6342</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. DUBLJEVIC</t>
+          <t>J. WRIGHT-FOREMAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4915</v>
+        <v>-4.0765</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2931</v>
+        <v>-1.5858</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1985</v>
+        <v>-2.4907</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0852</v>
+        <v>0.0617</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4418</v>
+        <v>0.6382</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6433</v>
+        <v>-0.5765</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7379</v>
+        <v>1.1901</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7379</v>
+        <v>0.4234</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3472</v>
+        <v>-1.1284</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7039</v>
+        <v>0.2148</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6433</v>
+        <v>-1.3432</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.2763</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2763</v>
+        <v>-3.6421</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.13</v>
+        <v>-0.4553</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2788</v>
+        <v>-0.2232</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1488</v>
+        <v>-0.232</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. BELL-HAYNES</t>
+          <t>B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5466</v>
+        <v>-4.2477</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0242</v>
+        <v>-2.9865</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.5224</v>
+        <v>-1.2612</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3651</v>
+        <v>-2.0852</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0235</v>
+        <v>-1.4418</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.3886</v>
+        <v>-0.6433</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4512</v>
+        <v>-0.7379</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2059</v>
+        <v>-0.7379</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2453</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.8163</v>
+        <v>-1.3472</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8176</v>
+        <v>-0.7039</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.6339</v>
+        <v>-0.6433</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4553</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.5039</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>2.9592</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4578</v>
+        <v>0.1138</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3943</v>
+        <v>0.0278</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8522</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1789</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6342</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.8132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. WRIGHT-FOREMAN</t>
+          <t>T. BELL-HAYNES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8709</v>
+        <v>-4.306</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1293</v>
+        <v>-0.1914</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7416</v>
+        <v>-4.1146</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0617</v>
+        <v>-2.3651</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6382</v>
+        <v>1.0235</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5765</v>
+        <v>-3.3886</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1901</v>
+        <v>0.4512</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4234</v>
+        <v>0.2059</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.2453</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1284</v>
+        <v>-2.8163</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2148</v>
+        <v>0.8176</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3432</v>
+        <v>-3.6339</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.0487</v>
+        <v>0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.6421</v>
+        <v>-2.5039</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5934</v>
+        <v>2.9592</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2497</v>
+        <v>-0.2173</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7667</v>
+        <v>0.2271</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4829</v>
+        <v>-0.4444</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.6342</v>
+        <v>-2.1789</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0895</v>
+        <v>1.6342</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.7237</v>
+        <v>-3.8132</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.7034</v>
+        <v>-7.006300000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1852</v>
+        <v>0.8822999999999992</v>
       </c>
       <c r="F13" t="n">
         <v>-7.8886</v>
@@ -1441,7 +1441,7 @@
         <v>-17.6042</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.08499999999999974</v>
+        <v>-0.08499999999999958</v>
       </c>
       <c r="K13" t="n">
         <v>-2.2877</v>
@@ -1459,7 +1459,7 @@
         <v>-19.8067</v>
       </c>
       <c r="P13" t="n">
-        <v>5.690900000000001</v>
+        <v>5.690899999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.6578</v>
@@ -1468,13 +1468,13 @@
         <v>19.3487</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6263999999999998</v>
+        <v>1.3234</v>
       </c>
       <c r="T13" t="n">
-        <v>0.06589999999999974</v>
+        <v>0.7628</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5606000000000003</v>
+        <v>0.5606000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>5.4475</v>
@@ -1483,7 +1483,7 @@
         <v>13.8626</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.415199999999999</v>
+        <v>-8.4152</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7829</v>
+        <v>5.4065</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8225</v>
+        <v>4.4148</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9604</v>
+        <v>0.9917</v>
       </c>
       <c r="G14" t="n">
         <v>5.5504</v>
@@ -1546,13 +1546,13 @@
         <v>1.5934</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6293</v>
+        <v>-0.0057</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6273</v>
+        <v>-0.0351</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.002</v>
+        <v>0.0294</v>
       </c>
       <c r="V14" t="n">
         <v>0.5447</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8226</v>
+        <v>3.1119</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0819</v>
+        <v>3.3712</v>
       </c>
       <c r="F15" t="n">
         <v>-0.2593</v>
@@ -1624,10 +1624,10 @@
         <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6132</v>
+        <v>-0.0975</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6034</v>
+        <v>-0.1072</v>
       </c>
       <c r="U15" t="n">
         <v>0.0097</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9152</v>
+        <v>2.3576</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2296</v>
+        <v>1.7034</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6856</v>
+        <v>0.6542</v>
       </c>
       <c r="G16" t="n">
         <v>4.1496</v>
@@ -1702,13 +1702,13 @@
         <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9173</v>
+        <v>-0.4749</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9061</v>
+        <v>-0.4324</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0112</v>
+        <v>-0.0425</v>
       </c>
       <c r="V16" t="n">
         <v>-1.0895</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4167</v>
+        <v>1.5838</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1892</v>
+        <v>-0.8338</v>
       </c>
       <c r="F17" t="n">
-        <v>2.6058</v>
+        <v>2.4176</v>
       </c>
       <c r="G17" t="n">
         <v>3.4558</v>
@@ -1780,13 +1780,13 @@
         <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2372</v>
+        <v>0.4043</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6273</v>
+        <v>-0.272</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8645</v>
+        <v>0.6763</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. DIAGNE</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2251</v>
+        <v>1.2391</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0477</v>
+        <v>2.2238</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2728</v>
+        <v>-0.9847</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1919</v>
+        <v>1.1264</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1985</v>
+        <v>-0.0177</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3903</v>
+        <v>1.144</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0917</v>
+        <v>2.0011</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0172</v>
+        <v>0.5861</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0745</v>
+        <v>1.415</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1002</v>
+        <v>-0.8747</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2157</v>
+        <v>-0.6037</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3159</v>
+        <v>-0.271</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1277</v>
+        <v>0.36</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1394</v>
+        <v>0.2228</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0117</v>
+        <v>0.1372</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1609</v>
+        <v>-0.7025</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.1609</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. LOPEZ DE LA TORRE</t>
+          <t>M. DIAGNE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7451</v>
+        <v>1.1938</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4674</v>
+        <v>-0.0477</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2777</v>
+        <v>1.2415</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.1919</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.204</v>
+        <v>-0.1985</v>
       </c>
       <c r="I19" t="n">
-        <v>1.144</v>
+        <v>0.3903</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7252</v>
+        <v>0.0917</v>
       </c>
       <c r="K19" t="n">
-        <v>0.055</v>
+        <v>0.0172</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6703</v>
+        <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2148</v>
+        <v>0.1002</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.259</v>
+        <v>-0.2157</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4738</v>
+        <v>0.3159</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6829</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1382</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4553</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6014</v>
+        <v>-0.159</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2091</v>
+        <v>-0.1394</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3923</v>
+        <v>-0.0196</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0895</v>
+        <v>1.1609</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0895</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.1609</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>J. HANDS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4657</v>
+        <v>0.7494</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5131</v>
+        <v>-0.8489</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0475</v>
+        <v>1.5983</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1264</v>
+        <v>-1.0777</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0177</v>
+        <v>-0.0377</v>
       </c>
       <c r="I20" t="n">
-        <v>1.144</v>
+        <v>-1.04</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0011</v>
+        <v>-1.4388</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5861</v>
+        <v>-1.2001</v>
       </c>
       <c r="L20" t="n">
-        <v>1.415</v>
+        <v>-0.2388</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8747</v>
+        <v>0.3611</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6037</v>
+        <v>1.1623</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.271</v>
+        <v>-0.8012</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4553</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4553</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4134</v>
+        <v>-0.3518</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4879</v>
+        <v>-0.2232</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0745</v>
+        <v>-0.1286</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7025</v>
+        <v>2.1789</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. HANDS</t>
+          <t>R. LOPEZ DE LA TORRE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2443</v>
+        <v>0.7138</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3227</v>
+        <v>0.4674</v>
       </c>
       <c r="F21" t="n">
-        <v>1.567</v>
+        <v>0.2463</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0777</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0377</v>
+        <v>-0.204</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.04</v>
+        <v>1.144</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4388</v>
+        <v>0.7252</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2001</v>
+        <v>0.055</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.2388</v>
+        <v>0.6703</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3611</v>
+        <v>0.2148</v>
       </c>
       <c r="N21" t="n">
-        <v>1.1623</v>
+        <v>-0.259</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8012</v>
+        <v>0.4738</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3658</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3658</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.857</v>
+        <v>-0.6328</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.697</v>
+        <v>-0.2091</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1599</v>
+        <v>-0.4237</v>
       </c>
       <c r="V21" t="n">
-        <v>2.1789</v>
+        <v>1.0895</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1789</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. RADEBAUGH</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2665</v>
+        <v>-1.2668</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4477</v>
+        <v>1.0093</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7143</v>
+        <v>-2.2761</v>
       </c>
       <c r="G22" t="n">
-        <v>1.7778</v>
+        <v>0.3303</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1919</v>
+        <v>-0.3387</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5858</v>
+        <v>0.669</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4889</v>
+        <v>0.8747</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4244</v>
+        <v>0.0927</v>
       </c>
       <c r="L22" t="n">
-        <v>1.9133</v>
+        <v>0.782</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2889</v>
+        <v>-0.5444</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6163999999999999</v>
+        <v>-0.4314</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3275</v>
+        <v>-0.113</v>
       </c>
       <c r="P22" t="n">
+        <v>0.2276</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-1.1382</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>-2.5039</v>
       </c>
       <c r="R22" t="n">
         <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2728</v>
+        <v>0.3542</v>
       </c>
       <c r="T22" t="n">
-        <v>1.4628</v>
+        <v>0.1833</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.19</v>
+        <v>0.171</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1789</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1789</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>J. RADEBAUGH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8661</v>
+        <v>-1.3953</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1277</v>
+        <v>-0.6183</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9938</v>
+        <v>-0.777</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3303</v>
+        <v>1.7778</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3387</v>
+        <v>0.1919</v>
       </c>
       <c r="I23" t="n">
-        <v>0.669</v>
+        <v>1.5858</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8747</v>
+        <v>1.4889</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0927</v>
+        <v>-0.4244</v>
       </c>
       <c r="L23" t="n">
-        <v>0.782</v>
+        <v>1.9133</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.5444</v>
+        <v>0.2889</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4314</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.113</v>
+        <v>-0.3275</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2276</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1382</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
         <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>0.755</v>
+        <v>0.144</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3017</v>
+        <v>0.3968</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4533</v>
+        <v>-0.2527</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1789</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0895</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.2684</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7318</v>
+        <v>-2.6307</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.4903</v>
+        <v>-1.6088</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2415</v>
+        <v>-1.0219</v>
       </c>
       <c r="G24" t="n">
         <v>0.3324</v>
@@ -2326,13 +2326,13 @@
         <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3601</v>
+        <v>-0.2589</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0229</v>
+        <v>-0.0955</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.383</v>
+        <v>-0.1634</v>
       </c>
       <c r="V24" t="n">
         <v>-2.0212</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.0499</v>
+        <v>-3.3599</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.841</v>
+        <v>-2.4333</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2089</v>
+        <v>-0.9266</v>
       </c>
       <c r="G25" t="n">
         <v>0.6394</v>
@@ -2404,13 +2404,13 @@
         <v>1.3658</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4017</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7428</v>
+        <v>0.1506</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3412</v>
+        <v>-0.0589</v>
       </c>
       <c r="V25" t="n">
         <v>-2.9529</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>7.7033</v>
+        <v>7.703199999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>6.798999999999999</v>
+        <v>6.7991</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9039999999999997</v>
+        <v>0.9039999999999996</v>
       </c>
       <c r="G26" t="n">
         <v>19.4679</v>
       </c>
       <c r="H26" t="n">
-        <v>1.863499999999999</v>
+        <v>1.8635</v>
       </c>
       <c r="I26" t="n">
         <v>17.6041</v>
@@ -2458,13 +2458,13 @@
         <v>19.3826</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.4238999999999999</v>
+        <v>-0.4239</v>
       </c>
       <c r="L26" t="n">
         <v>19.8067</v>
       </c>
       <c r="M26" t="n">
-        <v>0.08529999999999982</v>
+        <v>0.08529999999999988</v>
       </c>
       <c r="N26" t="n">
         <v>2.2877</v>
@@ -2482,13 +2482,13 @@
         <v>13.6581</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6263000000000001</v>
+        <v>-0.6263</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5604999999999994</v>
+        <v>-0.5604</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0658999999999999</v>
+        <v>-0.06579999999999997</v>
       </c>
       <c r="V26" t="n">
         <v>-5.4474</v>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104753_W33.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104753_W33.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-3.8132</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.4152</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>1.1609</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104753_W33.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-12.773</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
